--- a/reports/pdf_change_20261021.xlsx
+++ b/reports/pdf_change_20261021.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,644억   ·   현금 141억(3.2%)      당일 2026-10-21  vs  전영업일 2026-10-20      매수 8종목  /  매도 2종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,470억      당일 2026-10-21  vs  전영업일 2026-10-20      매수 8종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>144</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1467144531</v>
+        <v>1467144768</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-95</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1258752356</v>
+        <v>-1258752559</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>63</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>821600938</v>
+        <v>821601070</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-32</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-289134825</v>
+        <v>-289134871</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>52</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1292200468</v>
+        <v>1292200676</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>33</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1407206310</v>
+        <v>1407206536</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>29</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>457757046</v>
+        <v>457757119</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>21</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1298363270</v>
+        <v>1298363479</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1277787463</v>
+        <v>1277787668</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>420462152</v>
+        <v>420462220</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,166억   ·   현금 59억(1.9%)      당일 2026-10-21  vs  전영업일 2026-10-20      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,109억      당일 2026-10-21  vs  전영업일 2026-10-20      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -943,7 +943,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,403억   ·   현금 40억(1.7%)      당일 2026-10-21  vs  전영업일 2026-10-20      매수 3종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,290억      당일 2026-10-21  vs  전영업일 2026-10-20      매수 3종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1039,7 +1039,7 @@
         <v>15</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1769415215</v>
+        <v>1769415483</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>-50</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-831987601</v>
+        <v>-831987727</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>7</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>560018268</v>
+        <v>560018353</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>-25</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-768558843</v>
+        <v>-768558960</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>7</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>913835411</v>
+        <v>913835550</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>-14</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1039770326</v>
+        <v>-1039770484</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>-8</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-694322484</v>
+        <v>-694322590</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,071억   ·   현금 5억(0.3%)      당일 2026-10-21  vs  전영업일 2026-10-20      매수 3종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,073억      당일 2026-10-21  vs  전영업일 2026-10-20      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1288,7 +1288,7 @@
         <v>53</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1996700386</v>
+        <v>2027738324</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>-252</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-4041650762</v>
+        <v>-4104476666</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>14</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>2045413576</v>
+        <v>2077208742</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>-148</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1259672139</v>
+        <v>-1279253257</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>5369258887</v>
+        <v>5452721947</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억   ·   현금 3억(1.1%)      당일 2026-10-21  vs  전영업일 2026-10-20      매수 5종목  /  매도 5종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 269억      당일 2026-10-21  vs  전영업일 2026-10-20      매수 5종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1493,7 +1493,7 @@
         <v>61</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>111983733</v>
+        <v>105853332</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1514,11 +1514,11 @@
         <v>-34</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-92828445</v>
+        <v>-86905726</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>8.27%→7.93%</t>
+          <t>8.12%→7.78%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
@@ -1537,11 +1537,11 @@
         <v>34</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>32347581</v>
+        <v>29887369</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>0.30%→0.42%</t>
+          <t>0.29%→0.41%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -1558,7 +1558,7 @@
         <v>-22</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-50926670</v>
+        <v>-47462814</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1581,11 +1581,11 @@
         <v>24</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>55073967</v>
+        <v>52742416</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>1.30%→1.50%</t>
+          <t>1.31%→1.50%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -1602,11 +1602,11 @@
         <v>-19</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-30042782</v>
+        <v>-29024409</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>4.83%→4.71%</t>
+          <t>4.89%→4.77%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
@@ -1625,11 +1625,11 @@
         <v>7</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>39395976</v>
+        <v>36816511</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>1.17%→1.31%</t>
+          <t>1.15%→1.28%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -1646,11 +1646,11 @@
         <v>-6</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-50732370</v>
+        <v>-48802815</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>2.76%→2.57%</t>
+          <t>2.78%→2.60%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1669,7 +1669,7 @@
         <v>6</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>25165185</v>
+        <v>23597407</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>-3</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-8321395</v>
+        <v>-8160602</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1819,11 +1819,11 @@
         <v>3</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>105123799</v>
+        <v>101068761</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>3.48%→3.60%</t>
+          <t>3.38%→3.50%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -1847,11 +1847,11 @@
         <v>3</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>286617488</v>
+        <v>274636693</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>7.24%→7.60%</t>
+          <t>7.02%→7.36%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -1868,7 +1868,7 @@
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 860억   ·   현금 4억(0.4%)      당일 2026-10-21  vs  전영업일 2026-10-20      매수 5종목  /  매도 5종목</t>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 835억      당일 2026-10-21  vs  전영업일 2026-10-20      매수 5종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B50" s="4" t="n"/>
@@ -1964,7 +1964,7 @@
         <v>183</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>814331900</v>
+        <v>819327500</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>-85</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-302039074</v>
+        <v>-303891963</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>56</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>116929709</v>
+        <v>117647026</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>-85</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-191614697</v>
+        <v>-192790176</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>50</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>129748032</v>
+        <v>130543984</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>-66</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-346407685</v>
+        <v>-348532757</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>46</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>211818552</v>
+        <v>213117974</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>-57</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-256431663</v>
+        <v>-258004769</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>31</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>258713663</v>
+        <v>260300768</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>-34</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-365772090</v>
+        <v>-368015955</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2273,11 +2273,11 @@
         <v>57</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>768473820</v>
+        <v>785551016</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>2.79%→5.35%</t>
+          <t>2.96%→5.66%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -2294,11 +2294,11 @@
         <v>-46</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-113599733</v>
+        <v>-110646534</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.70%</t>
+          <t>1.06%→0.70%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -2317,11 +2317,11 @@
         <v>13</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>327719523</v>
+        <v>316591526</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>1.04%→2.13%</t>
+          <t>1.05%→2.13%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -2338,11 +2338,11 @@
         <v>-42</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-255259140</v>
+        <v>-235845065</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>0.81%→0.00%</t>
+          <t>0.78%→0.00%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2361,11 +2361,11 @@
         <v>12</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>209291951</v>
+        <v>195938354</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>3.89%→4.65%</t>
+          <t>3.78%→4.51%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>0.99%→0.00%</t>
+          <t>1.03%→0.00%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -2410,11 +2410,11 @@
         <v>-24</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-198249554</v>
+        <v>-205439952</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.00%</t>
+          <t>0.68%→0.00%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -2438,11 +2438,11 @@
         <v>-23</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-80720781</v>
+        <v>-76192542</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>0.26%→0.00%</t>
+          <t>0.25%→0.00%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -2466,11 +2466,11 @@
         <v>-21</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-178321878</v>
+        <v>-175984999</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>1.19%→0.63%</t>
+          <t>1.22%→0.65%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -2494,11 +2494,11 @@
         <v>-11</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-120760172</v>
+        <v>-113462773</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>0.94%→0.57%</t>
+          <t>0.92%→0.56%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
@@ -2522,11 +2522,11 @@
         <v>-7</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-378095112</v>
+        <v>-363714315</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>2.93%→1.76%</t>
+          <t>2.92%→1.75%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -2550,11 +2550,11 @@
         <v>-4</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-192942355</v>
+        <v>-182841557</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>1.08%→0.47%</t>
+          <t>1.06%→0.46%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">

--- a/reports/pdf_change_20261021.xlsx
+++ b/reports/pdf_change_20261021.xlsx
@@ -1076,23 +1076,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>560018353</v>
+        <v>913835550</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>1.34%→1.60%</t>
+          <t>6.43%→6.79%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>38→45</t>
+          <t>110→117</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1120,23 +1120,23 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>913835550</v>
+        <v>560018353</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>6.43%→6.79%</t>
+          <t>1.34%→1.60%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>110→117</t>
+          <t>38→45</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">

--- a/reports/pdf_change_20261021.xlsx
+++ b/reports/pdf_change_20261021.xlsx
@@ -1076,23 +1076,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>913835550</v>
+        <v>560018353</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>6.43%→6.79%</t>
+          <t>1.34%→1.60%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>110→117</t>
+          <t>38→45</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1120,23 +1120,23 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>560018353</v>
+        <v>913835550</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>1.34%→1.60%</t>
+          <t>6.43%→6.79%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>38→45</t>
+          <t>110→117</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
@@ -1978,23 +1978,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>싸이맥스  (편출)</t>
+          <t>저스템</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-85</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-303891963</v>
+        <v>-192790176</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.00%</t>
+          <t>2.64%→2.34%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>85→0</t>
+          <t>942→857</t>
         </is>
       </c>
     </row>
@@ -2022,23 +2022,23 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>저스템</t>
+          <t>싸이맥스  (편출)</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-85</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-192790176</v>
+        <v>-303891963</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>2.64%→2.34%</t>
+          <t>0.35%→0.00%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>942→857</t>
+          <t>85→0</t>
         </is>
       </c>
     </row>
